--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\sesi2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F969406-96CD-491E-8668-C7DB0462D7A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34596568-F1B4-43E1-93E4-AEF8722B532A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3023" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3055" uniqueCount="104">
   <si>
     <t>Aluno</t>
   </si>
@@ -783,6 +783,7 @@
     <col min="75" max="75" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="76" max="76" width="6.85546875" bestFit="1" customWidth="1"/>
     <col min="81" max="88" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="89" max="89" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:123" x14ac:dyDescent="0.25">
@@ -1041,7 +1042,9 @@
       <c r="CJ1" s="5">
         <v>45989</v>
       </c>
-      <c r="CK1" s="5"/>
+      <c r="CK1" s="5">
+        <v>45992</v>
+      </c>
       <c r="CL1" s="5"/>
     </row>
     <row r="2" spans="1:123" x14ac:dyDescent="0.25">
@@ -1309,6 +1312,9 @@
       <c r="CJ2" s="6" t="s">
         <v>39</v>
       </c>
+      <c r="CK2" s="6" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="3" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A3">
@@ -1575,7 +1581,9 @@
       <c r="CJ3" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="CK3" s="6"/>
+      <c r="CK3" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CL3" s="6"/>
       <c r="CM3" s="6"/>
       <c r="CN3" s="6"/>
@@ -1876,7 +1884,9 @@
       <c r="CJ4" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CK4" s="6"/>
+      <c r="CK4" s="6" t="s">
+        <v>34</v>
+      </c>
       <c r="CL4" s="6"/>
       <c r="CM4" s="6"/>
       <c r="CN4" s="6"/>
@@ -2177,7 +2187,9 @@
       <c r="CJ5" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CK5" s="6"/>
+      <c r="CK5" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CL5" s="6"/>
       <c r="CM5" s="6"/>
       <c r="CN5" s="6"/>
@@ -2478,7 +2490,9 @@
       <c r="CJ6" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CK6" s="6"/>
+      <c r="CK6" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CL6" s="6"/>
       <c r="CM6" s="6"/>
       <c r="CN6" s="6"/>
@@ -2779,7 +2793,9 @@
       <c r="CJ7" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CK7" s="6"/>
+      <c r="CK7" s="6" t="s">
+        <v>34</v>
+      </c>
       <c r="CL7" s="6"/>
       <c r="CM7" s="6"/>
       <c r="CN7" s="6"/>
@@ -3080,7 +3096,9 @@
       <c r="CJ8" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CK8" s="6"/>
+      <c r="CK8" s="6" t="s">
+        <v>34</v>
+      </c>
       <c r="CL8" s="6"/>
       <c r="CM8" s="6"/>
       <c r="CN8" s="6"/>
@@ -3381,7 +3399,9 @@
       <c r="CJ9" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CK9" s="6"/>
+      <c r="CK9" s="6" t="s">
+        <v>34</v>
+      </c>
       <c r="CL9" s="6"/>
       <c r="CM9" s="6"/>
       <c r="CN9" s="6"/>
@@ -3682,7 +3702,9 @@
       <c r="CJ10" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CK10" s="6"/>
+      <c r="CK10" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CL10" s="6"/>
       <c r="CM10" s="6"/>
       <c r="CN10" s="6"/>
@@ -3983,7 +4005,9 @@
       <c r="CJ11" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CK11" s="6"/>
+      <c r="CK11" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CL11" s="6"/>
       <c r="CM11" s="6"/>
       <c r="CN11" s="6"/>
@@ -4284,7 +4308,9 @@
       <c r="CJ12" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CK12" s="6"/>
+      <c r="CK12" s="6" t="s">
+        <v>34</v>
+      </c>
       <c r="CL12" s="6"/>
       <c r="CM12" s="6"/>
       <c r="CN12" s="6"/>
@@ -4585,7 +4611,9 @@
       <c r="CJ13" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CK13" s="6"/>
+      <c r="CK13" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CL13" s="6"/>
       <c r="CM13" s="6"/>
       <c r="CN13" s="6"/>
@@ -4886,7 +4914,9 @@
       <c r="CJ14" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CK14" s="6"/>
+      <c r="CK14" s="6" t="s">
+        <v>34</v>
+      </c>
       <c r="CL14" s="6"/>
       <c r="CM14" s="6"/>
       <c r="CN14" s="6"/>
@@ -5187,7 +5217,9 @@
       <c r="CJ15" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CK15" s="6"/>
+      <c r="CK15" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CL15" s="6"/>
       <c r="CM15" s="6"/>
       <c r="CN15" s="6"/>
@@ -5488,7 +5520,9 @@
       <c r="CJ16" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CK16" s="6"/>
+      <c r="CK16" s="6" t="s">
+        <v>34</v>
+      </c>
       <c r="CL16" s="6"/>
       <c r="CM16" s="6"/>
       <c r="CN16" s="6"/>
@@ -5789,7 +5823,9 @@
       <c r="CJ17" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CK17" s="6"/>
+      <c r="CK17" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CL17" s="6"/>
       <c r="CM17" s="6"/>
       <c r="CN17" s="6"/>
@@ -6090,7 +6126,9 @@
       <c r="CJ18" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CK18" s="6"/>
+      <c r="CK18" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CL18" s="6"/>
       <c r="CM18" s="6"/>
       <c r="CN18" s="6"/>
@@ -6391,7 +6429,9 @@
       <c r="CJ19" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CK19" s="6"/>
+      <c r="CK19" s="6" t="s">
+        <v>34</v>
+      </c>
       <c r="CL19" s="6"/>
       <c r="CM19" s="6"/>
       <c r="CN19" s="6"/>
@@ -6692,7 +6732,9 @@
       <c r="CJ20" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CK20" s="6"/>
+      <c r="CK20" s="6" t="s">
+        <v>34</v>
+      </c>
       <c r="CL20" s="6"/>
       <c r="CM20" s="6"/>
       <c r="CN20" s="6"/>
@@ -6993,7 +7035,9 @@
       <c r="CJ21" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CK21" s="6"/>
+      <c r="CK21" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CL21" s="6"/>
       <c r="CM21" s="6"/>
       <c r="CN21" s="6"/>
@@ -7294,7 +7338,9 @@
       <c r="CJ22" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CK22" s="6"/>
+      <c r="CK22" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CL22" s="6"/>
       <c r="CM22" s="6"/>
       <c r="CN22" s="6"/>
@@ -7595,7 +7641,9 @@
       <c r="CJ23" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="CK23" s="6"/>
+      <c r="CK23" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CL23" s="6"/>
       <c r="CM23" s="6"/>
       <c r="CN23" s="6"/>
@@ -7894,9 +7942,11 @@
         <v>35</v>
       </c>
       <c r="CJ24" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="CK24" s="6"/>
+        <v>34</v>
+      </c>
+      <c r="CK24" s="6" t="s">
+        <v>34</v>
+      </c>
       <c r="CL24" s="6"/>
       <c r="CM24" s="6"/>
       <c r="CN24" s="6"/>
@@ -8197,7 +8247,9 @@
       <c r="CJ25" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CK25" s="6"/>
+      <c r="CK25" s="6" t="s">
+        <v>34</v>
+      </c>
       <c r="CL25" s="6"/>
       <c r="CM25" s="6"/>
       <c r="CN25" s="6"/>
@@ -8498,7 +8550,9 @@
       <c r="CJ26" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CK26" s="6"/>
+      <c r="CK26" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CL26" s="6"/>
       <c r="CM26" s="6"/>
       <c r="CN26" s="6"/>
@@ -8799,7 +8853,9 @@
       <c r="CJ27" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CK27" s="6"/>
+      <c r="CK27" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CL27" s="6"/>
       <c r="CM27" s="6"/>
       <c r="CN27" s="6"/>
@@ -9100,7 +9156,9 @@
       <c r="CJ28" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CK28" s="6"/>
+      <c r="CK28" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CL28" s="6"/>
       <c r="CM28" s="6"/>
       <c r="CN28" s="6"/>
@@ -9401,7 +9459,9 @@
       <c r="CJ29" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CK29" s="6"/>
+      <c r="CK29" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CL29" s="6"/>
       <c r="CM29" s="6"/>
       <c r="CN29" s="6"/>
@@ -9702,7 +9762,9 @@
       <c r="CJ30" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CK30" s="6"/>
+      <c r="CK30" s="6" t="s">
+        <v>34</v>
+      </c>
       <c r="CL30" s="6"/>
       <c r="CM30" s="6"/>
       <c r="CN30" s="6"/>
@@ -10003,7 +10065,9 @@
       <c r="CJ31" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CK31" s="6"/>
+      <c r="CK31" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CL31" s="6"/>
       <c r="CM31" s="6"/>
       <c r="CN31" s="6"/>
@@ -10304,7 +10368,9 @@
       <c r="CJ32" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CK32" s="6"/>
+      <c r="CK32" s="6" t="s">
+        <v>34</v>
+      </c>
       <c r="CL32" s="6"/>
       <c r="CM32" s="6"/>
       <c r="CN32" s="6"/>
@@ -10605,7 +10671,9 @@
       <c r="CJ33" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CK33" s="6"/>
+      <c r="CK33" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CL33" s="6"/>
       <c r="CM33" s="6"/>
       <c r="CN33" s="6"/>
@@ -11286,7 +11354,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BE3:DG3 D3:AZ10 BB3:BB22 BE4:BJ10 D11:BA22 BC11:BJ22 D23:BJ33 A36:F43 BK4:DG33">
+  <conditionalFormatting sqref="BE3:DG3 D3:AZ10 BB3:BB22 BE4:BJ10 BK4:DG33 D11:BA22 BC11:BJ22 D23:BJ33 A36:F43">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\sesi2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34596568-F1B4-43E1-93E4-AEF8722B532A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB76BD7-8872-473E-B0BD-D082095C8346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2794,7 +2794,7 @@
         <v>35</v>
       </c>
       <c r="CK7" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="CL7" s="6"/>
       <c r="CM7" s="6"/>
@@ -10369,7 +10369,7 @@
         <v>35</v>
       </c>
       <c r="CK32" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="CL32" s="6"/>
       <c r="CM32" s="6"/>

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\sesi2025\ds\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrador\Desktop\sesi2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB76BD7-8872-473E-B0BD-D082095C8346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B4A93E8-A15B-46DE-A452-266F087B4613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3055" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3119" uniqueCount="104">
   <si>
     <t>Aluno</t>
   </si>
@@ -748,45 +748,46 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS43"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="12" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.7109375" customWidth="1"/>
-    <col min="14" max="14" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="22" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="12" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.6640625" customWidth="1"/>
+    <col min="14" max="14" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="22" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="6.6640625" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="9" bestFit="1" customWidth="1"/>
-    <col min="32" max="37" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="42" max="45" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="6.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="52" max="53" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="32" max="37" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="42" max="45" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="6.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="52" max="53" width="6.109375" bestFit="1" customWidth="1"/>
     <col min="54" max="62" width="7" bestFit="1" customWidth="1"/>
-    <col min="63" max="64" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="66" max="71" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="72" max="74" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="81" max="88" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="63" max="64" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="66" max="71" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="72" max="74" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="81" max="88" width="7.109375" bestFit="1" customWidth="1"/>
     <col min="89" max="89" width="7" bestFit="1" customWidth="1"/>
+    <col min="91" max="91" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
       <c r="D1" s="1">
         <v>45684</v>
       </c>
@@ -1045,9 +1046,14 @@
       <c r="CK1" s="5">
         <v>45992</v>
       </c>
-      <c r="CL1" s="5"/>
+      <c r="CL1" s="5">
+        <v>45996</v>
+      </c>
+      <c r="CM1" s="5">
+        <v>45999</v>
+      </c>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>41</v>
       </c>
@@ -1315,8 +1321,14 @@
       <c r="CK2" s="6" t="s">
         <v>33</v>
       </c>
+      <c r="CL2" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="CM2" s="6" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="3" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>24125208</v>
       </c>
@@ -1584,8 +1596,12 @@
       <c r="CK3" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CL3" s="6"/>
-      <c r="CM3" s="6"/>
+      <c r="CL3" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="CM3" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CN3" s="6"/>
       <c r="CO3" s="6"/>
       <c r="CP3" s="6"/>
@@ -1619,7 +1635,7 @@
       <c r="DR3" s="6"/>
       <c r="DS3" s="6"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>24125210</v>
       </c>
@@ -1861,7 +1877,7 @@
         <v>35</v>
       </c>
       <c r="CC4" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="CD4" s="6" t="s">
         <v>35</v>
@@ -1887,8 +1903,12 @@
       <c r="CK4" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="CL4" s="6"/>
-      <c r="CM4" s="6"/>
+      <c r="CL4" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="CM4" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CN4" s="6"/>
       <c r="CO4" s="6"/>
       <c r="CP4" s="6"/>
@@ -1922,7 +1942,7 @@
       <c r="DR4" s="6"/>
       <c r="DS4" s="6"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>24125230</v>
       </c>
@@ -2190,8 +2210,12 @@
       <c r="CK5" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CL5" s="6"/>
-      <c r="CM5" s="6"/>
+      <c r="CL5" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="CM5" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CN5" s="6"/>
       <c r="CO5" s="6"/>
       <c r="CP5" s="6"/>
@@ -2225,7 +2249,7 @@
       <c r="DR5" s="6"/>
       <c r="DS5" s="6"/>
     </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>24125329</v>
       </c>
@@ -2461,19 +2485,19 @@
         <v>35</v>
       </c>
       <c r="CA6" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="CB6" s="6" t="s">
         <v>35</v>
       </c>
       <c r="CC6" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="CD6" s="6" t="s">
         <v>34</v>
       </c>
       <c r="CE6" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="CF6" s="6" t="s">
         <v>34</v>
@@ -2493,8 +2517,12 @@
       <c r="CK6" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CL6" s="6"/>
-      <c r="CM6" s="6"/>
+      <c r="CL6" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="CM6" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CN6" s="6"/>
       <c r="CO6" s="6"/>
       <c r="CP6" s="6"/>
@@ -2528,7 +2556,7 @@
       <c r="DR6" s="6"/>
       <c r="DS6" s="6"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>24125304</v>
       </c>
@@ -2796,8 +2824,12 @@
       <c r="CK7" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CL7" s="6"/>
-      <c r="CM7" s="6"/>
+      <c r="CL7" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="CM7" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CN7" s="6"/>
       <c r="CO7" s="6"/>
       <c r="CP7" s="6"/>
@@ -2831,7 +2863,7 @@
       <c r="DR7" s="6"/>
       <c r="DS7" s="6"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>24125331</v>
       </c>
@@ -3099,8 +3131,12 @@
       <c r="CK8" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="CL8" s="6"/>
-      <c r="CM8" s="6"/>
+      <c r="CL8" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="CM8" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CN8" s="6"/>
       <c r="CO8" s="6"/>
       <c r="CP8" s="6"/>
@@ -3134,7 +3170,7 @@
       <c r="DR8" s="6"/>
       <c r="DS8" s="6"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>24125308</v>
       </c>
@@ -3376,7 +3412,7 @@
         <v>34</v>
       </c>
       <c r="CC9" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="CD9" s="6" t="s">
         <v>34</v>
@@ -3402,8 +3438,12 @@
       <c r="CK9" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="CL9" s="6"/>
-      <c r="CM9" s="6"/>
+      <c r="CL9" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="CM9" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CN9" s="6"/>
       <c r="CO9" s="6"/>
       <c r="CP9" s="6"/>
@@ -3437,7 +3477,7 @@
       <c r="DR9" s="6"/>
       <c r="DS9" s="6"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>24125247</v>
       </c>
@@ -3705,8 +3745,12 @@
       <c r="CK10" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CL10" s="6"/>
-      <c r="CM10" s="6"/>
+      <c r="CL10" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="CM10" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CN10" s="6"/>
       <c r="CO10" s="6"/>
       <c r="CP10" s="6"/>
@@ -3740,7 +3784,7 @@
       <c r="DR10" s="6"/>
       <c r="DS10" s="6"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>24125212</v>
       </c>
@@ -4008,8 +4052,12 @@
       <c r="CK11" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CL11" s="6"/>
-      <c r="CM11" s="6"/>
+      <c r="CL11" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="CM11" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CN11" s="6"/>
       <c r="CO11" s="6"/>
       <c r="CP11" s="6"/>
@@ -4043,7 +4091,7 @@
       <c r="DR11" s="6"/>
       <c r="DS11" s="6"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>24125232</v>
       </c>
@@ -4311,8 +4359,12 @@
       <c r="CK12" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="CL12" s="6"/>
-      <c r="CM12" s="6"/>
+      <c r="CL12" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="CM12" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CN12" s="6"/>
       <c r="CO12" s="6"/>
       <c r="CP12" s="6"/>
@@ -4346,7 +4398,7 @@
       <c r="DR12" s="6"/>
       <c r="DS12" s="6"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>24125214</v>
       </c>
@@ -4614,8 +4666,12 @@
       <c r="CK13" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CL13" s="6"/>
-      <c r="CM13" s="6"/>
+      <c r="CL13" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="CM13" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CN13" s="6"/>
       <c r="CO13" s="6"/>
       <c r="CP13" s="6"/>
@@ -4649,7 +4705,7 @@
       <c r="DR13" s="6"/>
       <c r="DS13" s="6"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>24125249</v>
       </c>
@@ -4917,8 +4973,12 @@
       <c r="CK14" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="CL14" s="6"/>
-      <c r="CM14" s="6"/>
+      <c r="CL14" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="CM14" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CN14" s="6"/>
       <c r="CO14" s="6"/>
       <c r="CP14" s="6"/>
@@ -4952,7 +5012,7 @@
       <c r="DR14" s="6"/>
       <c r="DS14" s="6"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>24125293</v>
       </c>
@@ -5220,8 +5280,12 @@
       <c r="CK15" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CL15" s="6"/>
-      <c r="CM15" s="6"/>
+      <c r="CL15" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="CM15" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CN15" s="6"/>
       <c r="CO15" s="6"/>
       <c r="CP15" s="6"/>
@@ -5255,7 +5319,7 @@
       <c r="DR15" s="6"/>
       <c r="DS15" s="6"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>24125310</v>
       </c>
@@ -5523,8 +5587,12 @@
       <c r="CK16" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="CL16" s="6"/>
-      <c r="CM16" s="6"/>
+      <c r="CL16" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="CM16" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CN16" s="6"/>
       <c r="CO16" s="6"/>
       <c r="CP16" s="6"/>
@@ -5558,7 +5626,7 @@
       <c r="DR16" s="6"/>
       <c r="DS16" s="6"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>24125295</v>
       </c>
@@ -5826,8 +5894,12 @@
       <c r="CK17" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CL17" s="6"/>
-      <c r="CM17" s="6"/>
+      <c r="CL17" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="CM17" s="6" t="s">
+        <v>34</v>
+      </c>
       <c r="CN17" s="6"/>
       <c r="CO17" s="6"/>
       <c r="CP17" s="6"/>
@@ -5861,7 +5933,7 @@
       <c r="DR17" s="6"/>
       <c r="DS17" s="6"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>24125251</v>
       </c>
@@ -6129,8 +6201,12 @@
       <c r="CK18" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CL18" s="6"/>
-      <c r="CM18" s="6"/>
+      <c r="CL18" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="CM18" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CN18" s="6"/>
       <c r="CO18" s="6"/>
       <c r="CP18" s="6"/>
@@ -6164,7 +6240,7 @@
       <c r="DR18" s="6"/>
       <c r="DS18" s="6"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>24125334</v>
       </c>
@@ -6432,8 +6508,12 @@
       <c r="CK19" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="CL19" s="6"/>
-      <c r="CM19" s="6"/>
+      <c r="CL19" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="CM19" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CN19" s="6"/>
       <c r="CO19" s="6"/>
       <c r="CP19" s="6"/>
@@ -6467,7 +6547,7 @@
       <c r="DR19" s="6"/>
       <c r="DS19" s="6"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>24125297</v>
       </c>
@@ -6735,8 +6815,12 @@
       <c r="CK20" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="CL20" s="6"/>
-      <c r="CM20" s="6"/>
+      <c r="CL20" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="CM20" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CN20" s="6"/>
       <c r="CO20" s="6"/>
       <c r="CP20" s="6"/>
@@ -6770,7 +6854,7 @@
       <c r="DR20" s="6"/>
       <c r="DS20" s="6"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>24125234</v>
       </c>
@@ -7038,8 +7122,12 @@
       <c r="CK21" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CL21" s="6"/>
-      <c r="CM21" s="6"/>
+      <c r="CL21" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="CM21" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CN21" s="6"/>
       <c r="CO21" s="6"/>
       <c r="CP21" s="6"/>
@@ -7073,7 +7161,7 @@
       <c r="DR21" s="6"/>
       <c r="DS21" s="6"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>24125216</v>
       </c>
@@ -7315,7 +7403,7 @@
         <v>34</v>
       </c>
       <c r="CC22" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="CD22" s="6" t="s">
         <v>35</v>
@@ -7341,8 +7429,12 @@
       <c r="CK22" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CL22" s="6"/>
-      <c r="CM22" s="6"/>
+      <c r="CL22" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="CM22" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CN22" s="6"/>
       <c r="CO22" s="6"/>
       <c r="CP22" s="6"/>
@@ -7376,7 +7468,7 @@
       <c r="DR22" s="6"/>
       <c r="DS22" s="6"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>24125236</v>
       </c>
@@ -7615,7 +7707,7 @@
         <v>35</v>
       </c>
       <c r="CB23" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="CC23" s="6" t="s">
         <v>35</v>
@@ -7644,8 +7736,12 @@
       <c r="CK23" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CL23" s="6"/>
-      <c r="CM23" s="6"/>
+      <c r="CL23" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="CM23" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CN23" s="6"/>
       <c r="CO23" s="6"/>
       <c r="CP23" s="6"/>
@@ -7679,7 +7775,7 @@
       <c r="DR23" s="6"/>
       <c r="DS23" s="6"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>24125238</v>
       </c>
@@ -7947,8 +8043,12 @@
       <c r="CK24" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="CL24" s="6"/>
-      <c r="CM24" s="6"/>
+      <c r="CL24" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="CM24" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CN24" s="6"/>
       <c r="CO24" s="6"/>
       <c r="CP24" s="6"/>
@@ -7982,7 +8082,7 @@
       <c r="DR24" s="6"/>
       <c r="DS24" s="6"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24125218</v>
       </c>
@@ -8250,8 +8350,12 @@
       <c r="CK25" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="CL25" s="6"/>
-      <c r="CM25" s="6"/>
+      <c r="CL25" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="CM25" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CN25" s="6"/>
       <c r="CO25" s="6"/>
       <c r="CP25" s="6"/>
@@ -8285,7 +8389,7 @@
       <c r="DR25" s="6"/>
       <c r="DS25" s="6"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>24125220</v>
       </c>
@@ -8553,8 +8657,12 @@
       <c r="CK26" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CL26" s="6"/>
-      <c r="CM26" s="6"/>
+      <c r="CL26" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="CM26" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CN26" s="6"/>
       <c r="CO26" s="6"/>
       <c r="CP26" s="6"/>
@@ -8588,7 +8696,7 @@
       <c r="DR26" s="6"/>
       <c r="DS26" s="6"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>24125299</v>
       </c>
@@ -8856,8 +8964,12 @@
       <c r="CK27" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CL27" s="6"/>
-      <c r="CM27" s="6"/>
+      <c r="CL27" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="CM27" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CN27" s="6"/>
       <c r="CO27" s="6"/>
       <c r="CP27" s="6"/>
@@ -8891,7 +9003,7 @@
       <c r="DR27" s="6"/>
       <c r="DS27" s="6"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>24125301</v>
       </c>
@@ -9159,8 +9271,12 @@
       <c r="CK28" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CL28" s="6"/>
-      <c r="CM28" s="6"/>
+      <c r="CL28" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="CM28" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CN28" s="6"/>
       <c r="CO28" s="6"/>
       <c r="CP28" s="6"/>
@@ -9194,7 +9310,7 @@
       <c r="DR28" s="6"/>
       <c r="DS28" s="6"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>24125316</v>
       </c>
@@ -9462,8 +9578,12 @@
       <c r="CK29" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CL29" s="6"/>
-      <c r="CM29" s="6"/>
+      <c r="CL29" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="CM29" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CN29" s="6"/>
       <c r="CO29" s="6"/>
       <c r="CP29" s="6"/>
@@ -9497,7 +9617,7 @@
       <c r="DR29" s="6"/>
       <c r="DS29" s="6"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>24125306</v>
       </c>
@@ -9765,8 +9885,12 @@
       <c r="CK30" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="CL30" s="6"/>
-      <c r="CM30" s="6"/>
+      <c r="CL30" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="CM30" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CN30" s="6"/>
       <c r="CO30" s="6"/>
       <c r="CP30" s="6"/>
@@ -9800,7 +9924,7 @@
       <c r="DR30" s="6"/>
       <c r="DS30" s="6"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>24125254</v>
       </c>
@@ -10068,8 +10192,12 @@
       <c r="CK31" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CL31" s="6"/>
-      <c r="CM31" s="6"/>
+      <c r="CL31" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="CM31" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CN31" s="6"/>
       <c r="CO31" s="6"/>
       <c r="CP31" s="6"/>
@@ -10103,7 +10231,7 @@
       <c r="DR31" s="6"/>
       <c r="DS31" s="6"/>
     </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>24125347</v>
       </c>
@@ -10371,8 +10499,12 @@
       <c r="CK32" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CL32" s="6"/>
-      <c r="CM32" s="6"/>
+      <c r="CL32" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="CM32" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CN32" s="6"/>
       <c r="CO32" s="6"/>
       <c r="CP32" s="6"/>
@@ -10406,7 +10538,7 @@
       <c r="DR32" s="6"/>
       <c r="DS32" s="6"/>
     </row>
-    <row r="33" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>24126394</v>
       </c>
@@ -10648,7 +10780,7 @@
         <v>35</v>
       </c>
       <c r="CC33" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="CD33" s="6" t="s">
         <v>35</v>
@@ -10674,8 +10806,12 @@
       <c r="CK33" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="CL33" s="6"/>
-      <c r="CM33" s="6"/>
+      <c r="CL33" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="CM33" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="CN33" s="6"/>
       <c r="CO33" s="6"/>
       <c r="CP33" s="6"/>
@@ -10709,7 +10845,7 @@
       <c r="DR33" s="6"/>
       <c r="DS33" s="6"/>
     </row>
-    <row r="34" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:123" x14ac:dyDescent="0.3">
       <c r="AZ34" s="6"/>
       <c r="BA34" s="6"/>
       <c r="BB34" s="6"/>
@@ -10783,7 +10919,7 @@
       <c r="DR34" s="6"/>
       <c r="DS34" s="6"/>
     </row>
-    <row r="35" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>55</v>
       </c>
@@ -10865,7 +11001,7 @@
       <c r="DR35" s="6"/>
       <c r="DS35" s="6"/>
     </row>
-    <row r="36" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:123" x14ac:dyDescent="0.3">
       <c r="C36" t="s">
         <v>42</v>
       </c>
@@ -10951,7 +11087,7 @@
       <c r="DR36" s="6"/>
       <c r="DS36" s="6"/>
     </row>
-    <row r="37" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>33</v>
       </c>
@@ -11038,7 +11174,7 @@
       <c r="DR37" s="6"/>
       <c r="DS37" s="6"/>
     </row>
-    <row r="38" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>39</v>
       </c>
@@ -11128,7 +11264,7 @@
       <c r="DR38" s="6"/>
       <c r="DS38" s="6"/>
     </row>
-    <row r="39" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:123" x14ac:dyDescent="0.3">
       <c r="C39">
         <f>B37*C37</f>
         <v>160</v>
@@ -11218,7 +11354,7 @@
       <c r="DR39" s="6"/>
       <c r="DS39" s="6"/>
     </row>
-    <row r="40" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:123" x14ac:dyDescent="0.3">
       <c r="AZ40" s="6"/>
       <c r="BA40" s="6"/>
       <c r="BB40" s="6"/>
@@ -11292,7 +11428,7 @@
       <c r="DR40" s="6"/>
       <c r="DS40" s="6"/>
     </row>
-    <row r="41" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>33</v>
       </c>
@@ -11306,7 +11442,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>39</v>
       </c>
@@ -11323,7 +11459,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:123" x14ac:dyDescent="0.3">
       <c r="C43">
         <f>B41*C41</f>
         <v>160</v>
@@ -11354,7 +11490,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BE3:DG3 D3:AZ10 BB3:BB22 BE4:BJ10 BK4:DG33 D11:BA22 BC11:BJ22 D23:BJ33 A36:F43">
+  <conditionalFormatting sqref="BE3:DG3 D3:AZ10 BB3:BB22 BE4:BJ10 D11:BA22 BC11:BJ22 D23:BJ33 A36:F43 BK4:DG33">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -11367,15 +11503,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>41</v>
       </c>
@@ -11389,7 +11525,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>24125208</v>
       </c>
@@ -11404,7 +11540,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>24125210</v>
       </c>
@@ -11419,7 +11555,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>24125230</v>
       </c>
@@ -11434,7 +11570,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>24125329</v>
       </c>
@@ -11449,7 +11585,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>24125304</v>
       </c>
@@ -11464,7 +11600,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>24125331</v>
       </c>
@@ -11479,7 +11615,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>24125308</v>
       </c>
@@ -11494,7 +11630,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>24125247</v>
       </c>
@@ -11509,7 +11645,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>24125212</v>
       </c>
@@ -11524,7 +11660,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>24125232</v>
       </c>
@@ -11539,7 +11675,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>24125214</v>
       </c>
@@ -11554,7 +11690,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>24125249</v>
       </c>
@@ -11569,7 +11705,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>24125293</v>
       </c>
@@ -11584,7 +11720,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>24125310</v>
       </c>
@@ -11599,7 +11735,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>24125295</v>
       </c>
@@ -11614,7 +11750,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>24125251</v>
       </c>
@@ -11629,7 +11765,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>24125334</v>
       </c>
@@ -11641,7 +11777,7 @@
         <v>24125334,Lohaine Vitória de Mattos Silva</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>24125297</v>
       </c>
@@ -11656,7 +11792,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>24125234</v>
       </c>
@@ -11671,7 +11807,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>24125216</v>
       </c>
@@ -11686,7 +11822,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>24125236</v>
       </c>
@@ -11701,7 +11837,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>24125238</v>
       </c>
@@ -11716,7 +11852,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>24125218</v>
       </c>
@@ -11731,7 +11867,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24125220</v>
       </c>
@@ -11746,7 +11882,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>24125299</v>
       </c>
@@ -11761,7 +11897,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>24125301</v>
       </c>
@@ -11776,7 +11912,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>24125316</v>
       </c>
@@ -11791,7 +11927,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>24125306</v>
       </c>
@@ -11803,7 +11939,7 @@
         <v>24125306,Miriam Bordini Mendonça</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>24125254</v>
       </c>
@@ -11818,7 +11954,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>24125347</v>
       </c>
@@ -11833,7 +11969,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>24126394</v>
       </c>
@@ -11857,18 +11993,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AE312F0-9CBD-47F5-A7D3-C25410349714}">
   <dimension ref="A1:I34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="10.7109375" customWidth="1"/>
-    <col min="7" max="7" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="10.6640625" customWidth="1"/>
+    <col min="7" max="7" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>59</v>
       </c>
@@ -11888,7 +12024,7 @@
       </c>
       <c r="I1" s="11"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>62</v>
       </c>
@@ -11914,7 +12050,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>60</v>
       </c>
@@ -11943,7 +12079,7 @@
         <v>45912</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -11972,7 +12108,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -11998,7 +12134,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -12024,7 +12160,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -12035,7 +12171,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -12043,7 +12179,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -12060,7 +12196,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -12077,7 +12213,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -12106,7 +12242,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -12135,7 +12271,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -12149,7 +12285,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -12172,7 +12308,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -12201,7 +12337,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -12227,7 +12363,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -12247,7 +12383,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -12273,7 +12409,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -12284,7 +12420,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -12307,12 +12443,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>10</v>
       </c>
@@ -12332,7 +12468,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>5</v>
       </c>
@@ -12346,13 +12482,13 @@
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>11</v>
       </c>
       <c r="B24" s="7"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>12</v>
       </c>
@@ -12360,7 +12496,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>6</v>
       </c>
@@ -12386,7 +12522,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>7</v>
       </c>
@@ -12400,7 +12536,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>20</v>
       </c>
@@ -12423,7 +12559,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>21</v>
       </c>
@@ -12452,7 +12588,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>26</v>
       </c>
@@ -12472,7 +12608,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>23</v>
       </c>
@@ -12486,7 +12622,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>16</v>
       </c>
@@ -12512,7 +12648,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>30</v>
       </c>
@@ -12532,7 +12668,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>32</v>
       </c>
